--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>81.80946273120468</v>
+        <v>13.29403769382076</v>
       </c>
       <c r="D2" t="n">
-        <v>72.48209346647783</v>
+        <v>11.77834018830265</v>
       </c>
       <c r="E2" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F2" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>101.8802689716939</v>
+        <v>16.55554370790027</v>
       </c>
       <c r="D3" t="n">
-        <v>101.219144787297</v>
+        <v>16.44811102793576</v>
       </c>
       <c r="E3" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F3" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>84.28868657056674</v>
+        <v>13.69691156771709</v>
       </c>
       <c r="D4" t="n">
-        <v>72.95592422764445</v>
+        <v>11.85533768699222</v>
       </c>
       <c r="E4" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F4" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>112.7486065685096</v>
+        <v>18.32164856738282</v>
       </c>
       <c r="D5" t="n">
-        <v>100.0377727076935</v>
+        <v>16.25613806500019</v>
       </c>
       <c r="E5" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F5" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>86.15795498808544</v>
+        <v>14.00066768556388</v>
       </c>
       <c r="D6" t="n">
-        <v>73.7418888574325</v>
+        <v>11.98305693933278</v>
       </c>
       <c r="E6" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F6" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>84.12795366472072</v>
+        <v>13.67079247051712</v>
       </c>
       <c r="D7" t="n">
-        <v>82.52257064950682</v>
+        <v>13.40991773054486</v>
       </c>
       <c r="E7" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F7" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>96.06725397628588</v>
+        <v>15.61092877114646</v>
       </c>
       <c r="D8" t="n">
-        <v>96.10534826624743</v>
+        <v>15.61711909326521</v>
       </c>
       <c r="E8" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F8" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>71.37620856442734</v>
+        <v>11.59863389171944</v>
       </c>
       <c r="D9" t="n">
-        <v>60.57389033381322</v>
+        <v>9.843257179244649</v>
       </c>
       <c r="E9" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F9" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>71.48307751194582</v>
+        <v>11.6160000956912</v>
       </c>
       <c r="D10" t="n">
-        <v>65.83695991245</v>
+        <v>10.69850598577312</v>
       </c>
       <c r="E10" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F10" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>91.75138291843054</v>
+        <v>14.90959972424496</v>
       </c>
       <c r="D11" t="n">
-        <v>79.06599328016655</v>
+        <v>12.84822390802707</v>
       </c>
       <c r="E11" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F11" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>97.76683815535789</v>
+        <v>15.88711120024566</v>
       </c>
       <c r="D12" t="n">
-        <v>85.05876470541247</v>
+        <v>13.82204926462953</v>
       </c>
       <c r="E12" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F12" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>65.56500455180232</v>
+        <v>10.65431323966788</v>
       </c>
       <c r="D13" t="n">
-        <v>56.8721008342001</v>
+        <v>9.241716385557517</v>
       </c>
       <c r="E13" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F13" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>70.13413646389816</v>
+        <v>11.39679717538345</v>
       </c>
       <c r="D14" t="n">
-        <v>62.94856549036125</v>
+        <v>10.2291418921837</v>
       </c>
       <c r="E14" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F14" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>77.77393628525459</v>
+        <v>12.63826464635387</v>
       </c>
       <c r="D15" t="n">
-        <v>76.7348039983912</v>
+        <v>12.46940564973857</v>
       </c>
       <c r="E15" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F15" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>68.60814128653772</v>
+        <v>11.14882295906238</v>
       </c>
       <c r="D16" t="n">
-        <v>65.93217039356519</v>
+        <v>10.71397768895434</v>
       </c>
       <c r="E16" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F16" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>63.45890697204526</v>
+        <v>10.31207238295736</v>
       </c>
       <c r="D17" t="n">
-        <v>52.2139637985911</v>
+        <v>8.484769117271055</v>
       </c>
       <c r="E17" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F17" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>96.76379290715828</v>
+        <v>15.72411634741322</v>
       </c>
       <c r="D18" t="n">
-        <v>84.17676679327235</v>
+        <v>13.67872460390676</v>
       </c>
       <c r="E18" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F18" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>63.10792345748377</v>
+        <v>10.25503756184111</v>
       </c>
       <c r="D19" t="n">
-        <v>59.12325261924577</v>
+        <v>9.607528550627437</v>
       </c>
       <c r="E19" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F19" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>73.60816185124396</v>
+        <v>11.96132630082714</v>
       </c>
       <c r="D20" t="n">
-        <v>60.98383891578877</v>
+        <v>9.909873823815674</v>
       </c>
       <c r="E20" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F20" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>68.13038779837213</v>
+        <v>11.07118801723547</v>
       </c>
       <c r="D21" t="n">
-        <v>55.72491915039672</v>
+        <v>9.055299361939468</v>
       </c>
       <c r="E21" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F21" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>57.13076163917056</v>
+        <v>9.283748766365216</v>
       </c>
       <c r="D22" t="n">
-        <v>46.78004288686228</v>
+        <v>7.601756969115121</v>
       </c>
       <c r="E22" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F22" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>63.00634282601261</v>
+        <v>10.23853070922705</v>
       </c>
       <c r="D23" t="n">
-        <v>51.07684134081559</v>
+        <v>8.299986717882534</v>
       </c>
       <c r="E23" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F23" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>57.38807656251809</v>
+        <v>9.32556244140919</v>
       </c>
       <c r="D24" t="n">
-        <v>48.78625290344409</v>
+        <v>7.927766096809665</v>
       </c>
       <c r="E24" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F24" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>56.21529140966913</v>
+        <v>9.134984854071234</v>
       </c>
       <c r="D25" t="n">
-        <v>50.4020387754622</v>
+        <v>8.190331301012607</v>
       </c>
       <c r="E25" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F25" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>80.73710419758467</v>
+        <v>13.11977943210751</v>
       </c>
       <c r="D26" t="n">
-        <v>68.02762906661323</v>
+        <v>11.05448972332465</v>
       </c>
       <c r="E26" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F26" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>56.17960201030657</v>
+        <v>9.129185326674817</v>
       </c>
       <c r="D27" t="n">
-        <v>53.8384072831758</v>
+        <v>8.748741183516067</v>
       </c>
       <c r="E27" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F27" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>64.67705731076809</v>
+        <v>10.51002181299982</v>
       </c>
       <c r="D28" t="n">
-        <v>64.6718553876277</v>
+        <v>10.5091765004895</v>
       </c>
       <c r="E28" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F28" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>47.00494613772415</v>
+        <v>7.638303747380174</v>
       </c>
       <c r="D29" t="n">
-        <v>38.88231277882553</v>
+        <v>6.318375826559149</v>
       </c>
       <c r="E29" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F29" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>73.35300992328781</v>
+        <v>11.91986411253427</v>
       </c>
       <c r="D30" t="n">
-        <v>74.71243529371617</v>
+        <v>12.14077073522888</v>
       </c>
       <c r="E30" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F30" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>93.28445487426038</v>
+        <v>15.15872391706731</v>
       </c>
       <c r="D31" t="n">
-        <v>81.03492149104837</v>
+        <v>13.16817474229536</v>
       </c>
       <c r="E31" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F31" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>49.23906116801619</v>
+        <v>8.001347439802631</v>
       </c>
       <c r="D32" t="n">
-        <v>38.0306526501699</v>
+        <v>6.179981055652608</v>
       </c>
       <c r="E32" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F32" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>49.37889722623533</v>
+        <v>8.024070799263242</v>
       </c>
       <c r="D33" t="n">
-        <v>44.96656607756258</v>
+        <v>7.30706698760392</v>
       </c>
       <c r="E33" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F33" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>80.15433363876164</v>
+        <v>13.02507921629877</v>
       </c>
       <c r="D34" t="n">
-        <v>67.7156783052065</v>
+        <v>11.00379772459606</v>
       </c>
       <c r="E34" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F34" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>71.90946258955405</v>
+        <v>11.68528767080253</v>
       </c>
       <c r="D35" t="n">
-        <v>59.37448357475263</v>
+        <v>9.648353580897302</v>
       </c>
       <c r="E35" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F35" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>51.75019663566714</v>
+        <v>8.409406953295912</v>
       </c>
       <c r="D36" t="n">
-        <v>39.31564276291541</v>
+        <v>6.388791948973754</v>
       </c>
       <c r="E36" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F36" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>36.72021638057905</v>
+        <v>5.967035161844096</v>
       </c>
       <c r="D37" t="n">
-        <v>28.00163399986316</v>
+        <v>4.550265524977764</v>
       </c>
       <c r="E37" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F37" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>52.8061121918618</v>
+        <v>8.580993231177542</v>
       </c>
       <c r="D38" t="n">
-        <v>54.33228221708572</v>
+        <v>8.82899586027643</v>
       </c>
       <c r="E38" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F38" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>37.85501801477424</v>
+        <v>6.151440427400814</v>
       </c>
       <c r="D39" t="n">
-        <v>26.24439064647489</v>
+        <v>4.264713480052169</v>
       </c>
       <c r="E39" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F39" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>37.42349865383726</v>
+        <v>6.081318531248554</v>
       </c>
       <c r="D40" t="n">
-        <v>36.62808200526849</v>
+        <v>5.95206332585613</v>
       </c>
       <c r="E40" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F40" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>74.72849786106293</v>
+        <v>12.14338090242273</v>
       </c>
       <c r="D41" t="n">
-        <v>63.14682329391196</v>
+        <v>10.2613587852607</v>
       </c>
       <c r="E41" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F41" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>49.46905026145836</v>
+        <v>8.038720667486984</v>
       </c>
       <c r="D42" t="n">
-        <v>53.48334335718798</v>
+        <v>8.691043295543048</v>
       </c>
       <c r="E42" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F42" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>67.00884254627364</v>
+        <v>10.88893691376947</v>
       </c>
       <c r="D43" t="n">
-        <v>72.09384372538074</v>
+        <v>11.71524960537437</v>
       </c>
       <c r="E43" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F43" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>86.61145573662452</v>
+        <v>14.07436155720148</v>
       </c>
       <c r="D44" t="n">
-        <v>75.51641773480561</v>
+        <v>12.27141788190591</v>
       </c>
       <c r="E44" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F44" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>63.4820155642402</v>
+        <v>10.31582752918903</v>
       </c>
       <c r="D45" t="n">
-        <v>52.33384799667119</v>
+        <v>8.504250299459068</v>
       </c>
       <c r="E45" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F45" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>60.49322404633531</v>
+        <v>9.830148907529487</v>
       </c>
       <c r="D46" t="n">
-        <v>66.96384344470569</v>
+        <v>10.88162455976467</v>
       </c>
       <c r="E46" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F46" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>24.61990769104879</v>
+        <v>4.000734999795429</v>
       </c>
       <c r="D47" t="n">
-        <v>12.52905711064039</v>
+        <v>2.035971780479063</v>
       </c>
       <c r="E47" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F47" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>66.52745035674653</v>
+        <v>10.81071068297131</v>
       </c>
       <c r="D48" t="n">
-        <v>73.30844725645225</v>
+        <v>11.91262267917349</v>
       </c>
       <c r="E48" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F48" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>32.25839132595694</v>
+        <v>5.241988590468003</v>
       </c>
       <c r="D49" t="n">
-        <v>36.07395672016489</v>
+        <v>5.862017967026794</v>
       </c>
       <c r="E49" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F49" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>19.16736373060762</v>
+        <v>3.114696606223738</v>
       </c>
       <c r="D50" t="n">
-        <v>11.95405461577751</v>
+        <v>1.942533875063845</v>
       </c>
       <c r="E50" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F50" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>42.26696180427851</v>
+        <v>6.868381293195258</v>
       </c>
       <c r="D51" t="n">
-        <v>48.55071723294241</v>
+        <v>7.889491550353142</v>
       </c>
       <c r="E51" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F51" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>20.23753938185923</v>
+        <v>3.288600149552124</v>
       </c>
       <c r="D52" t="n">
-        <v>7.568563491317212</v>
+        <v>1.229891567339047</v>
       </c>
       <c r="E52" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F52" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>13.9282024846087</v>
+        <v>2.263332903748913</v>
       </c>
       <c r="D53" t="n">
-        <v>3.632400362435174</v>
+        <v>0.5902650588957158</v>
       </c>
       <c r="E53" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F53" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>43.46343938651319</v>
+        <v>7.062808900308394</v>
       </c>
       <c r="D54" t="n">
-        <v>51.02286927961801</v>
+        <v>8.291216257937927</v>
       </c>
       <c r="E54" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F54" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>20.44237348362562</v>
+        <v>3.321885691089164</v>
       </c>
       <c r="D55" t="n">
-        <v>21.90205659598359</v>
+        <v>3.559084196847334</v>
       </c>
       <c r="E55" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F55" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>8.630615083467427</v>
+        <v>1.402474951063457</v>
       </c>
       <c r="D56" t="n">
-        <v>12.40841456045033</v>
+        <v>2.016367366073179</v>
       </c>
       <c r="E56" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F56" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>29.62575973914458</v>
+        <v>4.814185957610994</v>
       </c>
       <c r="D57" t="n">
-        <v>37.17845336229072</v>
+        <v>6.041498671372242</v>
       </c>
       <c r="E57" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F57" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>75.38111661705433</v>
+        <v>12.24943145027133</v>
       </c>
       <c r="D58" t="n">
-        <v>72.56624837835467</v>
+        <v>11.79201536148264</v>
       </c>
       <c r="E58" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F58" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>70.81918800696704</v>
+        <v>11.50811805113214</v>
       </c>
       <c r="D59" t="n">
-        <v>62.32049747365117</v>
+        <v>10.12708083946832</v>
       </c>
       <c r="E59" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F59" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>20.95843560700504</v>
+        <v>3.405745786138319</v>
       </c>
       <c r="D60" t="n">
-        <v>11.42629968724384</v>
+        <v>1.856773699177124</v>
       </c>
       <c r="E60" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F60" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>63.38594412281343</v>
+        <v>10.30021591995718</v>
       </c>
       <c r="D61" t="n">
-        <v>72.21480445554838</v>
+        <v>11.73490572402661</v>
       </c>
       <c r="E61" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F61" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>33.46519858638791</v>
+        <v>5.438094770288036</v>
       </c>
       <c r="D62" t="n">
-        <v>42.62123663280284</v>
+        <v>6.925950952830462</v>
       </c>
       <c r="E62" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F62" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>44.94130056385443</v>
+        <v>7.302961341626345</v>
       </c>
       <c r="D63" t="n">
-        <v>54.46928828217268</v>
+        <v>8.851259345853061</v>
       </c>
       <c r="E63" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F63" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>6.082172015006761</v>
+        <v>0.9883529524385987</v>
       </c>
       <c r="D64" t="n">
-        <v>14.32642240089734</v>
+        <v>2.328043640145817</v>
       </c>
       <c r="E64" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F64" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2496,16 +2496,16 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>27.83763728503503</v>
+        <v>4.523616058818193</v>
       </c>
       <c r="D65" t="n">
-        <v>38.57432892863839</v>
+        <v>6.26832845090374</v>
       </c>
       <c r="E65" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F65" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2528,16 +2528,16 @@
         <v>65</v>
       </c>
       <c r="C66" t="n">
-        <v>57.01506451475464</v>
+        <v>9.26494798364763</v>
       </c>
       <c r="D66" t="n">
-        <v>67.02082740862964</v>
+        <v>10.89088445390232</v>
       </c>
       <c r="E66" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F66" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2560,16 +2560,16 @@
         <v>66</v>
       </c>
       <c r="C67" t="n">
-        <v>47.66806475455773</v>
+        <v>7.746060522615631</v>
       </c>
       <c r="D67" t="n">
-        <v>36.10940546128231</v>
+        <v>5.867778387458376</v>
       </c>
       <c r="E67" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F67" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2592,16 +2592,16 @@
         <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>59.5074355688822</v>
+        <v>9.669958279943359</v>
       </c>
       <c r="D68" t="n">
-        <v>62.71920115921058</v>
+        <v>10.19187018837172</v>
       </c>
       <c r="E68" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F68" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2624,16 +2624,16 @@
         <v>68</v>
       </c>
       <c r="C69" t="n">
-        <v>51.09251789220357</v>
+        <v>8.30253415748308</v>
       </c>
       <c r="D69" t="n">
-        <v>44.37641942709339</v>
+        <v>7.211168156902676</v>
       </c>
       <c r="E69" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F69" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2656,16 +2656,16 @@
         <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>10.08719779297986</v>
+        <v>1.639169641359228</v>
       </c>
       <c r="D70" t="n">
-        <v>22.71959239170531</v>
+        <v>3.691933763652112</v>
       </c>
       <c r="E70" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F70" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2688,16 +2688,16 @@
         <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>13.46693971359241</v>
+        <v>2.188377703458767</v>
       </c>
       <c r="D71" t="n">
-        <v>19.3521743567287</v>
+        <v>3.144728332968414</v>
       </c>
       <c r="E71" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F71" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2720,16 +2720,16 @@
         <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>39.66136603926399</v>
+        <v>6.444971981380398</v>
       </c>
       <c r="D72" t="n">
-        <v>50.57105106157967</v>
+        <v>8.217795797506698</v>
       </c>
       <c r="E72" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F72" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2752,16 +2752,16 @@
         <v>72</v>
       </c>
       <c r="C73" t="n">
-        <v>37.75500304766955</v>
+        <v>6.135187995246302</v>
       </c>
       <c r="D73" t="n">
-        <v>50.00879985324441</v>
+        <v>8.126429976152217</v>
       </c>
       <c r="E73" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F73" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2784,16 +2784,16 @@
         <v>73</v>
       </c>
       <c r="C74" t="n">
-        <v>23.52170594393428</v>
+        <v>3.82227721588932</v>
       </c>
       <c r="D74" t="n">
-        <v>27.26833462748665</v>
+        <v>4.431104376966581</v>
       </c>
       <c r="E74" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F74" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         <v>74</v>
       </c>
       <c r="C75" t="n">
-        <v>53.23469817860335</v>
+        <v>8.650638454023046</v>
       </c>
       <c r="D75" t="n">
-        <v>74.98301215627458</v>
+        <v>12.18473947539462</v>
       </c>
       <c r="E75" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F75" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         <v>75</v>
       </c>
       <c r="C76" t="n">
-        <v>43.78942852582557</v>
+        <v>7.115782135446655</v>
       </c>
       <c r="D76" t="n">
-        <v>43.9191157705996</v>
+        <v>7.136856312722435</v>
       </c>
       <c r="E76" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F76" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2880,16 +2880,16 @@
         <v>76</v>
       </c>
       <c r="C77" t="n">
-        <v>27.74535975950051</v>
+        <v>4.508620960918834</v>
       </c>
       <c r="D77" t="n">
-        <v>39.80608373940523</v>
+        <v>6.468488607653351</v>
       </c>
       <c r="E77" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F77" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2912,16 +2912,16 @@
         <v>77</v>
       </c>
       <c r="C78" t="n">
-        <v>48.86046317255821</v>
+        <v>7.93982526554071</v>
       </c>
       <c r="D78" t="n">
-        <v>61.19630363283454</v>
+        <v>9.944399340335613</v>
       </c>
       <c r="E78" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F78" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2944,16 +2944,16 @@
         <v>78</v>
       </c>
       <c r="C79" t="n">
-        <v>38.13310441136221</v>
+        <v>6.19662946684636</v>
       </c>
       <c r="D79" t="n">
-        <v>57.16784016998628</v>
+        <v>9.289774027622771</v>
       </c>
       <c r="E79" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F79" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2976,16 +2976,16 @@
         <v>79</v>
       </c>
       <c r="C80" t="n">
-        <v>43.29466365336803</v>
+        <v>7.035382843672305</v>
       </c>
       <c r="D80" t="n">
-        <v>81.84112502896508</v>
+        <v>13.29918281720683</v>
       </c>
       <c r="E80" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F80" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3008,16 +3008,16 @@
         <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>37.95705601767224</v>
+        <v>6.168021602871739</v>
       </c>
       <c r="D81" t="n">
-        <v>50.66288388799932</v>
+        <v>8.232718631799891</v>
       </c>
       <c r="E81" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F81" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3040,16 +3040,16 @@
         <v>81</v>
       </c>
       <c r="C82" t="n">
-        <v>39.55139396789575</v>
+        <v>6.42710151978306</v>
       </c>
       <c r="D82" t="n">
-        <v>46.74213182942868</v>
+        <v>7.595596422282161</v>
       </c>
       <c r="E82" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F82" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3072,16 +3072,16 @@
         <v>82</v>
       </c>
       <c r="C83" t="n">
-        <v>64.57708216351496</v>
+        <v>10.49377585157118</v>
       </c>
       <c r="D83" t="n">
-        <v>76.85134652387605</v>
+        <v>12.48834381012986</v>
       </c>
       <c r="E83" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F83" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3104,16 +3104,16 @@
         <v>83</v>
       </c>
       <c r="C84" t="n">
-        <v>70.9743897010456</v>
+        <v>11.53333832641991</v>
       </c>
       <c r="D84" t="n">
-        <v>83.08368026276922</v>
+        <v>13.5010980427</v>
       </c>
       <c r="E84" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F84" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3136,16 +3136,16 @@
         <v>84</v>
       </c>
       <c r="C85" t="n">
-        <v>41.13774720456697</v>
+        <v>6.684883920742133</v>
       </c>
       <c r="D85" t="n">
-        <v>46.03265022229066</v>
+        <v>7.480305661122233</v>
       </c>
       <c r="E85" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F85" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3168,16 +3168,16 @@
         <v>85</v>
       </c>
       <c r="C86" t="n">
-        <v>30.00552046348733</v>
+        <v>4.875897075316692</v>
       </c>
       <c r="D86" t="n">
-        <v>64.34713350024886</v>
+        <v>10.45640919379044</v>
       </c>
       <c r="E86" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F86" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3200,16 +3200,16 @@
         <v>86</v>
       </c>
       <c r="C87" t="n">
-        <v>29.04050769480661</v>
+        <v>4.719082500406074</v>
       </c>
       <c r="D87" t="n">
-        <v>75.99883059917302</v>
+        <v>12.34980997236562</v>
       </c>
       <c r="E87" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F87" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3232,16 +3232,16 @@
         <v>87</v>
       </c>
       <c r="C88" t="n">
-        <v>39.83369932346233</v>
+        <v>6.472976140062629</v>
       </c>
       <c r="D88" t="n">
-        <v>49.46883799099805</v>
+        <v>8.038686173537185</v>
       </c>
       <c r="E88" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F88" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3264,16 +3264,16 @@
         <v>88</v>
       </c>
       <c r="C89" t="n">
-        <v>23.55564966269813</v>
+        <v>3.827793070188446</v>
       </c>
       <c r="D89" t="n">
-        <v>68.93167504924915</v>
+        <v>11.20139719550299</v>
       </c>
       <c r="E89" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F89" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3296,16 +3296,16 @@
         <v>89</v>
       </c>
       <c r="C90" t="n">
-        <v>50.74753383587375</v>
+        <v>8.246474248329486</v>
       </c>
       <c r="D90" t="n">
-        <v>63.40345630100463</v>
+        <v>10.30306164891325</v>
       </c>
       <c r="E90" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F90" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3328,16 +3328,16 @@
         <v>90</v>
       </c>
       <c r="C91" t="n">
-        <v>24.88005564791739</v>
+        <v>4.043009042786577</v>
       </c>
       <c r="D91" t="n">
-        <v>61.77754698119909</v>
+        <v>10.03885138444485</v>
       </c>
       <c r="E91" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F91" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3360,16 +3360,16 @@
         <v>91</v>
       </c>
       <c r="C92" t="n">
-        <v>41.13694242010401</v>
+        <v>6.684753143266902</v>
       </c>
       <c r="D92" t="n">
-        <v>53.45426497786522</v>
+        <v>8.686318058903099</v>
       </c>
       <c r="E92" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F92" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3392,16 +3392,16 @@
         <v>92</v>
       </c>
       <c r="C93" t="n">
-        <v>29.56543676885927</v>
+        <v>4.804383474939632</v>
       </c>
       <c r="D93" t="n">
-        <v>57.67857932947587</v>
+        <v>9.372769141039829</v>
       </c>
       <c r="E93" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F93" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3424,16 +3424,16 @@
         <v>93</v>
       </c>
       <c r="C94" t="n">
-        <v>65.90154251323214</v>
+        <v>10.70900065840022</v>
       </c>
       <c r="D94" t="n">
-        <v>78.54704709390209</v>
+        <v>12.76389515275909</v>
       </c>
       <c r="E94" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F94" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3456,16 +3456,16 @@
         <v>94</v>
       </c>
       <c r="C95" t="n">
-        <v>16.13436385765376</v>
+        <v>2.621834126868736</v>
       </c>
       <c r="D95" t="n">
-        <v>74.62645954250372</v>
+        <v>12.12679967565686</v>
       </c>
       <c r="E95" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F95" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3488,16 +3488,16 @@
         <v>95</v>
       </c>
       <c r="C96" t="n">
-        <v>41.09799539323539</v>
+        <v>6.678424251400751</v>
       </c>
       <c r="D96" t="n">
-        <v>49.20775429172615</v>
+        <v>7.996260072405499</v>
       </c>
       <c r="E96" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F96" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>96</v>
       </c>
       <c r="C97" t="n">
-        <v>29.05391145624438</v>
+        <v>4.721260611639712</v>
       </c>
       <c r="D97" t="n">
-        <v>92.35327263532571</v>
+        <v>15.00740680324043</v>
       </c>
       <c r="E97" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F97" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3552,16 +3552,16 @@
         <v>97</v>
       </c>
       <c r="C98" t="n">
-        <v>65.52617135061851</v>
+        <v>10.64800284447551</v>
       </c>
       <c r="D98" t="n">
-        <v>78.15541192226232</v>
+        <v>12.70025443736763</v>
       </c>
       <c r="E98" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F98" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3584,16 +3584,16 @@
         <v>98</v>
       </c>
       <c r="C99" t="n">
-        <v>82.97641063884369</v>
+        <v>13.4836667288121</v>
       </c>
       <c r="D99" t="n">
-        <v>95.63838656871896</v>
+        <v>15.54123781741683</v>
       </c>
       <c r="E99" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F99" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3616,16 +3616,16 @@
         <v>99</v>
       </c>
       <c r="C100" t="n">
-        <v>54.68617579529192</v>
+        <v>8.886503566734937</v>
       </c>
       <c r="D100" t="n">
-        <v>64.85279314448418</v>
+        <v>10.53857888597868</v>
       </c>
       <c r="E100" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F100" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3648,16 +3648,16 @@
         <v>100</v>
       </c>
       <c r="C101" t="n">
-        <v>76.73608443448165</v>
+        <v>12.46961372060327</v>
       </c>
       <c r="D101" t="n">
-        <v>89.43416806527004</v>
+        <v>14.53305231060638</v>
       </c>
       <c r="E101" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F101" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3680,16 +3680,16 @@
         <v>101</v>
       </c>
       <c r="C102" t="n">
-        <v>12.67168319554979</v>
+        <v>2.059148519276841</v>
       </c>
       <c r="D102" t="n">
-        <v>88.88349478945038</v>
+        <v>14.44356790328569</v>
       </c>
       <c r="E102" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F102" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3712,16 +3712,16 @@
         <v>102</v>
       </c>
       <c r="C103" t="n">
-        <v>48.34452518629721</v>
+        <v>7.855985342773297</v>
       </c>
       <c r="D103" t="n">
-        <v>66.07343706861963</v>
+        <v>10.73693352365069</v>
       </c>
       <c r="E103" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F103" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3744,16 +3744,16 @@
         <v>103</v>
       </c>
       <c r="C104" t="n">
-        <v>76.56580095740651</v>
+        <v>12.44194265557856</v>
       </c>
       <c r="D104" t="n">
-        <v>89.18189949324282</v>
+        <v>14.49205866765196</v>
       </c>
       <c r="E104" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F104" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3776,16 +3776,16 @@
         <v>104</v>
       </c>
       <c r="C105" t="n">
-        <v>66.32787330842517</v>
+        <v>10.77827941261909</v>
       </c>
       <c r="D105" t="n">
-        <v>78.27001176513014</v>
+        <v>12.71887691183365</v>
       </c>
       <c r="E105" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F105" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3808,16 +3808,16 @@
         <v>105</v>
       </c>
       <c r="C106" t="n">
-        <v>16.64988674128619</v>
+        <v>2.705606595459007</v>
       </c>
       <c r="D106" t="n">
-        <v>98.45040435049637</v>
+        <v>15.99819070695566</v>
       </c>
       <c r="E106" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F106" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -3840,16 +3840,16 @@
         <v>106</v>
       </c>
       <c r="C107" t="n">
-        <v>6.31499683206565</v>
+        <v>1.026186985210668</v>
       </c>
       <c r="D107" t="n">
-        <v>81.82066938211429</v>
+        <v>13.29585877459357</v>
       </c>
       <c r="E107" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F107" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3872,16 +3872,16 @@
         <v>107</v>
       </c>
       <c r="C108" t="n">
-        <v>16.03049262308147</v>
+        <v>2.604955051250739</v>
       </c>
       <c r="D108" t="n">
-        <v>79.12019887326461</v>
+        <v>12.8570323169055</v>
       </c>
       <c r="E108" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F108" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -3904,16 +3904,16 @@
         <v>108</v>
       </c>
       <c r="C109" t="n">
-        <v>35.29071355541594</v>
+        <v>5.73474095275509</v>
       </c>
       <c r="D109" t="n">
-        <v>71.29529352614736</v>
+        <v>11.58548519799895</v>
       </c>
       <c r="E109" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F109" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3936,16 +3936,16 @@
         <v>109</v>
       </c>
       <c r="C110" t="n">
-        <v>51.61205579655193</v>
+        <v>8.386959066939689</v>
       </c>
       <c r="D110" t="n">
-        <v>73.54752642219357</v>
+        <v>11.95147304360646</v>
       </c>
       <c r="E110" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F110" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -3968,16 +3968,16 @@
         <v>110</v>
       </c>
       <c r="C111" t="n">
-        <v>64.33924507402189</v>
+        <v>10.45512732452856</v>
       </c>
       <c r="D111" t="n">
-        <v>75.52337410743463</v>
+        <v>12.27254829245813</v>
       </c>
       <c r="E111" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F111" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4000,16 +4000,16 @@
         <v>111</v>
       </c>
       <c r="C112" t="n">
-        <v>87.6889011282038</v>
+        <v>14.24944643333312</v>
       </c>
       <c r="D112" t="n">
-        <v>100.3725513736459</v>
+        <v>16.31053959821745</v>
       </c>
       <c r="E112" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F112" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4032,16 +4032,16 @@
         <v>112</v>
       </c>
       <c r="C113" t="n">
-        <v>86.53616284224451</v>
+        <v>14.06212646186473</v>
       </c>
       <c r="D113" t="n">
-        <v>99.24446277160716</v>
+        <v>16.12722520038616</v>
       </c>
       <c r="E113" t="n">
-        <v>24.17613922189841</v>
+        <v>3.92862262355849</v>
       </c>
       <c r="F113" t="n">
-        <v>22.30311666823834</v>
+        <v>3.62425645858873</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
